--- a/ramales.xlsx
+++ b/ramales.xlsx
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="J2" s="59" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="3">

--- a/ramales.xlsx
+++ b/ramales.xlsx
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="J2" s="59" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="3">

--- a/ramales.xlsx
+++ b/ramales.xlsx
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="J2" s="59" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="3">

--- a/ramales.xlsx
+++ b/ramales.xlsx
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="J2" s="59" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="3">

--- a/ramales.xlsx
+++ b/ramales.xlsx
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="J2" s="59" t="n">
-        <v>46302</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="3">

--- a/ramales.xlsx
+++ b/ramales.xlsx
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="J2" s="59" t="n">
-        <v>46309</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="3">

--- a/ramales.xlsx
+++ b/ramales.xlsx
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="J2" s="59" t="n">
-        <v>46316</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="3">
